--- a/config/bms/BCU_永泰.xlsx
+++ b/config/bms/BCU_永泰.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18569" windowHeight="11268" activeTab="1"/>
+    <workbookView windowWidth="22010" windowHeight="12332" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="报文" sheetId="1" r:id="rId1"/>
@@ -453,13 +453,13 @@
 21930|清除系统锁</t>
   </si>
   <si>
-    <t>mainControl</t>
+    <t>mainCtl</t>
   </si>
   <si>
     <t>{"en":"Main control"}</t>
   </si>
   <si>
-    <t>insulationSampling</t>
+    <t>insulationSamp</t>
   </si>
   <si>
     <t>{"en":"Insulation sampling"}</t>
@@ -501,7 +501,7 @@
 4 停机|stop</t>
   </si>
   <si>
-    <t>operatingStatus</t>
+    <t>operatingSt</t>
   </si>
   <si>
     <t>{"en":"Operating status"}</t>
@@ -513,7 +513,7 @@
     <t>V</t>
   </si>
   <si>
-    <t>individualAccumulationAndTotalPressure</t>
+    <t>cellAccumAndTotalPressure</t>
   </si>
   <si>
     <t>{"en":"Individual accumulation and total pressure"}</t>
@@ -522,7 +522,7 @@
     <t>采集总压与累加总压差</t>
   </si>
   <si>
-    <t>collectTotalPressureAndAccumulateTotalPressureDifference</t>
+    <t>collectTotalPressureAndAccumDiff</t>
   </si>
   <si>
     <t>{"en":"Collect total pressure and accumulate total pressure difference"}</t>
@@ -540,7 +540,7 @@
     <t>单体最高电压</t>
   </si>
   <si>
-    <t>maximumVoltagePerUnit</t>
+    <t>maxVPerUnit</t>
   </si>
   <si>
     <t>{"en":"Maximum voltage per unit"}</t>
@@ -549,7 +549,7 @@
     <t>单体最高电压编号</t>
   </si>
   <si>
-    <t>maximumVoltageCodeOfIndividualUnit</t>
+    <t>maxVCodeOfCell</t>
   </si>
   <si>
     <t>{"en":"Maximum voltage code of individual unit"}</t>
@@ -558,7 +558,7 @@
     <t>最高单体所在从控号</t>
   </si>
   <si>
-    <t>theHighestUnitIsLocatedUnderTheControlNumber</t>
+    <t>highestUnitCtlNo</t>
   </si>
   <si>
     <t>{"en":"The highest unit is located under the control number"}</t>
@@ -567,7 +567,7 @@
     <t>最高单体在从控中的单体编号</t>
   </si>
   <si>
-    <t>theHighestMonomerNumberInTheControlSystem</t>
+    <t>highestCellNoInCtlSys</t>
   </si>
   <si>
     <t>{"en":"The highest monomer number in the control system"}</t>
@@ -576,7 +576,7 @@
     <t>单体最低电压</t>
   </si>
   <si>
-    <t>minimumVoltagePerUnit</t>
+    <t>minVPerUnit</t>
   </si>
   <si>
     <t>{"en":"Minimum voltage per unit"}</t>
@@ -585,7 +585,7 @@
     <t>单体最低电压编号</t>
   </si>
   <si>
-    <t>minimumVoltageCodeOfIndividualUnit</t>
+    <t>minVCodeOfCell</t>
   </si>
   <si>
     <t>{"en":"Minimum voltage code of individual unit"}</t>
@@ -594,7 +594,7 @@
     <t>最低单体所在从控编号</t>
   </si>
   <si>
-    <t>controlNumberOfTheLowestUnitLocation</t>
+    <t>lowestUnitCtlNo</t>
   </si>
   <si>
     <t>{"en":"Control number of the lowest unit location"}</t>
@@ -603,7 +603,7 @@
     <t>最低单体在从控中的单体编号</t>
   </si>
   <si>
-    <t>theLowestMonomerNumberInTheControlSystem</t>
+    <t>lowestCellNoInCtlSys</t>
   </si>
   <si>
     <t>{"en":"The lowest monomer number in the control system"}</t>
@@ -612,7 +612,7 @@
     <t>最高最低单体压差</t>
   </si>
   <si>
-    <t>maximumAndMinimumIndividualPressureDifference</t>
+    <t>maxAndMinCellPressureDiff</t>
   </si>
   <si>
     <t>{"en":"Maximum and minimum individual pressure difference"}</t>
@@ -621,7 +621,7 @@
     <t>单体平均电压</t>
   </si>
   <si>
-    <t>averageVoltagePerUnit</t>
+    <t>avgVPerUnit</t>
   </si>
   <si>
     <t>{"en":"Average voltage per unit"}</t>
@@ -636,7 +636,7 @@
     <t>℃</t>
   </si>
   <si>
-    <t>maximumTemperatureOfBattery</t>
+    <t>maxTOfBattery</t>
   </si>
   <si>
     <t>{"en":"Maximum temperature of battery"}</t>
@@ -645,7 +645,7 @@
     <t>电池最高温度编号</t>
   </si>
   <si>
-    <t>maximumTemperatureCodeOfBattery</t>
+    <t>maxTCodeOfBattery</t>
   </si>
   <si>
     <t>{"en":"Maximum temperature code of battery"}</t>
@@ -654,7 +654,7 @@
     <t>最高温度所在从控编号</t>
   </si>
   <si>
-    <t>controlNumberWhereTheHighestTemperatureIsLocated</t>
+    <t>highestTCtlNo</t>
   </si>
   <si>
     <t>{"en":"Control number where the highest temperature is located"}</t>
@@ -663,7 +663,7 @@
     <t>最高温度在从控中的温度编号</t>
   </si>
   <si>
-    <t>theTemperatureNumberOfTheHighestTemperatureInTheControlSystem</t>
+    <t>highestTNoInCtlSys</t>
   </si>
   <si>
     <t>{"en":"The temperature number of the highest temperature in the control system"}</t>
@@ -672,7 +672,7 @@
     <t>电池最低温度</t>
   </si>
   <si>
-    <t>minimumTemperatureOfBattery</t>
+    <t>minTOfBattery</t>
   </si>
   <si>
     <t>{"en":"Minimum temperature of battery"}</t>
@@ -681,7 +681,7 @@
     <t>电池最低温度编号</t>
   </si>
   <si>
-    <t>batteryMinimumTemperatureCode</t>
+    <t>batteryMinTCode</t>
   </si>
   <si>
     <t>{"en":"Battery minimum temperature code"}</t>
@@ -690,7 +690,7 @@
     <t>最低温度所在从控编号</t>
   </si>
   <si>
-    <t>controlNumberWhereTheLowestTemperatureIsLocated</t>
+    <t>lowestTCtlNo</t>
   </si>
   <si>
     <t>{"en":"Control number where the lowest temperature is located"}</t>
@@ -699,7 +699,7 @@
     <t>最低温度在从控中的温度编号</t>
   </si>
   <si>
-    <t>theTemperatureNumberOfTheLowestTemperatureInTheControlSystem</t>
+    <t>lowestTNoInCtlSys</t>
   </si>
   <si>
     <t>{"en":"The temperature number of the lowest temperature in the control system"}</t>
@@ -708,7 +708,7 @@
     <t>平均温度</t>
   </si>
   <si>
-    <t>averageTemperature</t>
+    <t>avgT</t>
   </si>
   <si>
     <t>{"en":"average temperature"}</t>
@@ -717,7 +717,7 @@
     <t>最大极柱温度</t>
   </si>
   <si>
-    <t>maximumPoleTemperature</t>
+    <t>maxPoleT</t>
   </si>
   <si>
     <t>{"en":"Maximum pole temperature"}</t>
@@ -726,7 +726,7 @@
     <t>最大极柱温度编号</t>
   </si>
   <si>
-    <t>maximumPoleTemperatureNumber</t>
+    <t>maxPoleTNo</t>
   </si>
   <si>
     <t>{"en":"Maximum Pole Temperature Number"}</t>
@@ -738,7 +738,7 @@
     <t>A</t>
   </si>
   <si>
-    <t>maximumAcceptableChargingCurrent</t>
+    <t>maxAcceptableChgI</t>
   </si>
   <si>
     <t>{"en":"Maximum acceptable charging current"}</t>
@@ -747,7 +747,7 @@
     <t>最大可接受放电电流</t>
   </si>
   <si>
-    <t>maximumAcceptableDischargeCurrent</t>
+    <t>maxAcceptableDischgI</t>
   </si>
   <si>
     <t>{"en":"Maximum acceptable discharge current"}</t>
@@ -807,7 +807,7 @@
     <t>kWh</t>
   </si>
   <si>
-    <t>rechargeableCapacity</t>
+    <t>rechargeableCap</t>
   </si>
   <si>
     <t>{"en":"Rechargeable capacity"}</t>
@@ -816,7 +816,7 @@
     <t>可放电量</t>
   </si>
   <si>
-    <t>dischargeCapacity</t>
+    <t>dischargeCap</t>
   </si>
   <si>
     <t>{"en":"discharge capacity"}</t>
@@ -843,7 +843,7 @@
     <t>累计充电电量高 16 位</t>
   </si>
   <si>
-    <t>accumulatedChargingCapacityIs16DigitsHigh</t>
+    <t>accumChgCapHigh16</t>
   </si>
   <si>
     <t>{"en":"Accumulated charging capacity is 16 digits high"}</t>
@@ -852,7 +852,7 @@
     <t>累计充电电量低 16 位</t>
   </si>
   <si>
-    <t>accumulatedChargingPowerIs16DigitsLow</t>
+    <t>accumChgPwrLow16</t>
   </si>
   <si>
     <t>{"en":"Accumulated charging power is 16 digits low"}</t>
@@ -861,7 +861,7 @@
     <t>累计放电电量高 16 位</t>
   </si>
   <si>
-    <t>accumulatedDischargeCapacityIs16DigitsHigh</t>
+    <t>accumDischgCapHigh16</t>
   </si>
   <si>
     <t>{"en":"Accumulated discharge capacity is 16 digits high"}</t>
@@ -870,7 +870,7 @@
     <t>累计放电电量低 16 位</t>
   </si>
   <si>
-    <t>accumulatedDischargePowerIs16DigitsLow</t>
+    <t>accumDischgPwrLow16</t>
   </si>
   <si>
     <t>{"en":"Accumulated discharge power is 16 digits low"}</t>
@@ -879,7 +879,7 @@
     <t>电池总电压</t>
   </si>
   <si>
-    <t>totalBatteryVoltage</t>
+    <t>totalBatteryV</t>
   </si>
   <si>
     <t>{"en":"Total battery voltage"}</t>
@@ -888,7 +888,7 @@
     <t>负载电压</t>
   </si>
   <si>
-    <t>loadVoltage</t>
+    <t>loadV</t>
   </si>
   <si>
     <t>{"en":"load voltage"}</t>
@@ -897,7 +897,7 @@
     <t>总电流</t>
   </si>
   <si>
-    <t>totalCurrent</t>
+    <t>totalI</t>
   </si>
   <si>
     <t>{"en":"total current"}</t>
@@ -909,7 +909,7 @@
     <t>kΩ</t>
   </si>
   <si>
-    <t>insulationResistance</t>
+    <t>insulationR</t>
   </si>
   <si>
     <t>{"en":"Insulation resistance"}</t>
@@ -918,7 +918,7 @@
     <t>正端绝缘阻值</t>
   </si>
   <si>
-    <t>positiveEndInsulationResistanceValue</t>
+    <t>posEndInsulationR</t>
   </si>
   <si>
     <t>{"en":"Positive end insulation resistance value"}</t>
@@ -927,7 +927,7 @@
     <t>负端绝缘阻值</t>
   </si>
   <si>
-    <t>negativeTerminalInsulationResistanceValue</t>
+    <t>negTerminalInsulationR</t>
   </si>
   <si>
     <t>{"en":"Negative terminal insulation resistance value"}</t>
@@ -939,7 +939,7 @@
     <t>°C</t>
   </si>
   <si>
-    <t>highPressureBoxTemperature1</t>
+    <t>highPressureBoxT1</t>
   </si>
   <si>
     <t>{"en":"High pressure box temperature 1"}</t>
@@ -948,7 +948,7 @@
     <t>高压箱温度 2</t>
   </si>
   <si>
-    <t>highPressureBoxTemperature2</t>
+    <t>highPressureBoxT2</t>
   </si>
   <si>
     <t>{"en":"High pressure box temperature 2"}</t>
@@ -957,7 +957,7 @@
     <t>高压箱温度 3</t>
   </si>
   <si>
-    <t>highPressureBoxTemperature3</t>
+    <t>highPressureBoxT3</t>
   </si>
   <si>
     <t>{"en":"High pressure box temperature 3"}</t>
@@ -966,7 +966,7 @@
     <t>高压箱温度 4</t>
   </si>
   <si>
-    <t>highPressureBoxTemperature4</t>
+    <t>highPressureBoxT4</t>
   </si>
   <si>
     <t>{"en":"High pressure box temperature 4"}</t>
@@ -975,7 +975,7 @@
     <t>其他报警信息</t>
   </si>
   <si>
-    <t>otherAlarmInformation</t>
+    <t>otherAlmInfo</t>
   </si>
   <si>
     <t>{"en":"Other alarm information"}</t>
@@ -1002,7 +1002,7 @@
     <t>Rack 接触器状态</t>
   </si>
   <si>
-    <t>rackContactorStatus</t>
+    <t>rackContactorSt</t>
   </si>
   <si>
     <t>{"en":"Rack contactor status"}</t>
@@ -1029,7 +1029,7 @@
     <t>主控EEP故障状态</t>
   </si>
   <si>
-    <t>mainControlEepFaultStatus</t>
+    <t>mainCtlEepFltSt</t>
   </si>
   <si>
     <t>{"en":"Main control EEP fault status"}</t>
@@ -1056,7 +1056,7 @@
     <t>从控详细故障报警</t>
   </si>
   <si>
-    <t>controlDetailedFaultAlarm</t>
+    <t>ctlDetailedFltAlm</t>
   </si>
   <si>
     <t>{"en":"Control detailed fault alarm"}</t>
@@ -1083,7 +1083,7 @@
     <t>功能安全告警详细故障</t>
   </si>
   <si>
-    <t>functionalSafetyAlarmDetailedFault</t>
+    <t>funcSafetyAlmDetailedFlt</t>
   </si>
   <si>
     <t>{"en":"Functional safety alarm detailed fault"}</t>
@@ -1110,7 +1110,7 @@
     <t>均衡错误类型高16位</t>
   </si>
   <si>
-    <t>balanceErrorTypeHigh16Bits</t>
+    <t>balanceErrTypeHigh16</t>
   </si>
   <si>
     <t>{"en":"Balance error type high 16 bits"}</t>
@@ -1137,7 +1137,7 @@
     <t>均衡错误类型低16位</t>
   </si>
   <si>
-    <t>balanceErrorTypeLow16Bits</t>
+    <t>balanceErrTypeLow16</t>
   </si>
   <si>
     <t>{"en":"Balance error type low 16 bits"}</t>
@@ -1164,7 +1164,7 @@
     <t>从控 1-16 被动均衡故障状态</t>
   </si>
   <si>
-    <t>passiveEquilibriumFaultStateFromControl116</t>
+    <t>passiveEquilibriumFltStFromCtl116</t>
   </si>
   <si>
     <t>{"en":"Passive equilibrium fault state from control 1-16"}</t>
@@ -1191,7 +1191,7 @@
     <t>从控 17-32 被动均衡故障状态</t>
   </si>
   <si>
-    <t>passiveBalancingFaultStateFromControl1732</t>
+    <t>passiveBalancingFltStFromCtl1732</t>
   </si>
   <si>
     <t>{"en":"Passive balancing fault state from control 17-32"}</t>
@@ -1218,7 +1218,7 @@
     <t>从控 33-48 被动均衡故障状态</t>
   </si>
   <si>
-    <t>control3348PassiveBalancingFaultState</t>
+    <t>ctl3348PassiveBalancingFltSt</t>
   </si>
   <si>
     <t>{"en":"Control 33-48 passive balancing fault state"}</t>
@@ -1245,7 +1245,7 @@
     <t>从控 49-64 被动均衡故障状态</t>
   </si>
   <si>
-    <t>control4964PassiveBalancingFaultState</t>
+    <t>ctl4964PassiveBalancingFltSt</t>
   </si>
   <si>
     <t>{"en":"Control 49-64 passive balancing fault state"}</t>
@@ -1272,7 +1272,7 @@
     <t>BMU 17-32 通信状态</t>
   </si>
   <si>
-    <t>bmu1732CommunicationStatus</t>
+    <t>bmu1732ComSt</t>
   </si>
   <si>
     <t>{"en":"BMU 17-32 communication status"}</t>
@@ -1299,7 +1299,7 @@
     <t>BMU 1-16 通信状态</t>
   </si>
   <si>
-    <t>bmu116CommunicationStatus</t>
+    <t>bmu116ComSt</t>
   </si>
   <si>
     <t>{"en":"BMU 1-16 communication status"}</t>
@@ -1326,7 +1326,7 @@
     <t>主控对外故障报警</t>
   </si>
   <si>
-    <t>mainControlExternalFaultAlarm</t>
+    <t>mainCtlExternalFltAlm</t>
   </si>
   <si>
     <t>{"en":"Main control external fault alarm"}</t>
@@ -1353,7 +1353,7 @@
     <t>Rack 严重报警</t>
   </si>
   <si>
-    <t>rackSeriousAlarm</t>
+    <t>rackSeriousAlm</t>
   </si>
   <si>
     <t>{"en":"Rack serious alarm"}</t>
@@ -1380,7 +1380,7 @@
     <t>Rack 中度报警</t>
   </si>
   <si>
-    <t>rackModerateAlarm</t>
+    <t>rackModerateAlm</t>
   </si>
   <si>
     <t>{"en":"Rack moderate alarm"}</t>
@@ -1407,7 +1407,7 @@
     <t>Rack 轻微报警</t>
   </si>
   <si>
-    <t>rackMinorAlarm</t>
+    <t>rackMinorAlm</t>
   </si>
   <si>
     <t>{"en":"Rack minor alarm"}</t>
@@ -1434,7 +1434,7 @@
     <t>BMU 33-48 概要故障</t>
   </si>
   <si>
-    <t>bmu3348SummaryFault</t>
+    <t>bmu3348SummaryFlt</t>
   </si>
   <si>
     <t>{"en":"BMU 33-48 Summary Fault"}</t>
@@ -1461,7 +1461,7 @@
     <t>BMU 17-32 概要故障</t>
   </si>
   <si>
-    <t>bmu1732SummaryFault</t>
+    <t>bmu1732SummaryFlt</t>
   </si>
   <si>
     <t>{"en":"BMU 17-32 Summary Fault"}</t>
@@ -1488,7 +1488,7 @@
     <t>BMU 1-16 概要故障</t>
   </si>
   <si>
-    <t>bmu116SummaryFault</t>
+    <t>bmu116SummaryFlt</t>
   </si>
   <si>
     <t>{"en":"BMU 1-16 Summary Fault"}</t>
@@ -1515,7 +1515,7 @@
     <t>BMU 33-48 通信故障</t>
   </si>
   <si>
-    <t>bmu3348CommunicationFailure</t>
+    <t>bmu3348ComFailure</t>
   </si>
   <si>
     <t>{"en":"BMU 33-48 communication failure"}</t>
@@ -1524,7 +1524,7 @@
     <t>功能安全告警详细故障 2</t>
   </si>
   <si>
-    <t>functionalSafetyAlarmDetailedFault2</t>
+    <t>funcSafetyAlmDetailedFlt2</t>
   </si>
   <si>
     <t>{"en":"Functional safety alarm detailed fault 2"}</t>
@@ -1551,7 +1551,7 @@
     <t>IO 状态(IO1-IO7)</t>
   </si>
   <si>
-    <t>ioStatusIo1Io7</t>
+    <t>ioStIo1Io7</t>
   </si>
   <si>
     <t>{"en":"IO Status (IO1-IO7)"}</t>
@@ -1560,7 +1560,7 @@
     <t>总电压过高严重报警</t>
   </si>
   <si>
-    <t>seriousAlarmDueToHighTotalVoltage</t>
+    <t>seriousAlmHighTotalV</t>
   </si>
   <si>
     <t>{"en":"Serious alarm due to high total voltage"}</t>
@@ -1569,7 +1569,7 @@
     <t>总电压过高中度报警</t>
   </si>
   <si>
-    <t>moderateAlarmDueToHighTotalVoltage</t>
+    <t>moderateAlmHighTotalV</t>
   </si>
   <si>
     <t>{"en":"Moderate alarm due to high total voltage"}</t>
@@ -1578,7 +1578,7 @@
     <t>总电压过高轻微报警</t>
   </si>
   <si>
-    <t>slightAlarmDueToHighTotalVoltage</t>
+    <t>slightAlmHighTotalV</t>
   </si>
   <si>
     <t>{"en":"Slight alarm due to high total voltage"}</t>
@@ -1587,7 +1587,7 @@
     <t>总电压过低严重报警</t>
   </si>
   <si>
-    <t>seriousAlarmForLowTotalVoltage</t>
+    <t>seriousAlmLowTotalV</t>
   </si>
   <si>
     <t>{"en":"Serious alarm for low total voltage"}</t>
@@ -1596,7 +1596,7 @@
     <t>总电压过低中度报警</t>
   </si>
   <si>
-    <t>moderateAlarmForLowTotalVoltage</t>
+    <t>moderateAlmLowTotalV</t>
   </si>
   <si>
     <t>{"en":"Moderate alarm for low total voltage"}</t>
@@ -1605,7 +1605,7 @@
     <t>总电压过低轻微报警</t>
   </si>
   <si>
-    <t>minorAlarmForLowTotalVoltage</t>
+    <t>minorAlmLowTotalV</t>
   </si>
   <si>
     <t>{"en":"Minor alarm for low total voltage"}</t>
@@ -1614,7 +1614,7 @@
     <t>总压差过大严重报警</t>
   </si>
   <si>
-    <t>seriousAlarmDueToExcessiveTotalPressureDifference</t>
+    <t>seriousAlmExcessTotalPressureDiff</t>
   </si>
   <si>
     <t>{"en":"Serious alarm due to excessive total pressure difference"}</t>
@@ -1623,7 +1623,7 @@
     <t>总压差过大中度报警</t>
   </si>
   <si>
-    <t>moderateAlarmDueToExcessiveTotalPressureDifference</t>
+    <t>moderateAlmExcessTotalPressureDiff</t>
   </si>
   <si>
     <t>{"en":"Moderate alarm due to excessive total pressure difference"}</t>
@@ -1632,7 +1632,7 @@
     <t>总压差过大轻微报警</t>
   </si>
   <si>
-    <t>minorAlarmDueToExcessiveTotalPressureDifference</t>
+    <t>minorAlmExcessTotalPressureDiff</t>
   </si>
   <si>
     <t>{"en":"Minor alarm due to excessive total pressure difference"}</t>
@@ -1644,7 +1644,7 @@
     <t>Ω/V</t>
   </si>
   <si>
-    <t>seriousAlarmDueToLowInsulationResistance</t>
+    <t>seriousAlmLowInsulationR</t>
   </si>
   <si>
     <t>{"en":"Serious alarm due to low insulation resistance"}</t>
@@ -1653,7 +1653,7 @@
     <t>绝缘阻值过低中度报警</t>
   </si>
   <si>
-    <t>moderateAlarmDueToLowInsulationResistance</t>
+    <t>moderateAlmLowInsulationR</t>
   </si>
   <si>
     <t>{"en":"Moderate alarm due to low insulation resistance"}</t>
@@ -1662,7 +1662,7 @@
     <t>绝缘阻值过低轻微报警</t>
   </si>
   <si>
-    <t>minorAlarmDueToLowInsulationResistance</t>
+    <t>minorAlmLowInsulationR</t>
   </si>
   <si>
     <t>{"en":"Minor alarm due to low insulation resistance"}</t>
@@ -1671,7 +1671,7 @@
     <t>SOC 过低严重报警</t>
   </si>
   <si>
-    <t>seriousAlarmForLowSoc</t>
+    <t>seriousAlmLowSoc</t>
   </si>
   <si>
     <t>{"en":"Serious alarm for low SOC"}</t>
@@ -1680,7 +1680,7 @@
     <t>SOC 过低中度报警</t>
   </si>
   <si>
-    <t>socLowModerateAlarm</t>
+    <t>socLowModerateAlm</t>
   </si>
   <si>
     <t>{"en":"SOC low moderate alarm"}</t>
@@ -1689,7 +1689,7 @@
     <t>SOC 过低轻微报警</t>
   </si>
   <si>
-    <t>socLowSlightAlarm</t>
+    <t>socLowSlightAlm</t>
   </si>
   <si>
     <t>{"en":"SOC low slight alarm"}</t>
@@ -1698,7 +1698,7 @@
     <t>SOC 过高严重报警</t>
   </si>
   <si>
-    <t>seriousAlarmDueToHighSoc</t>
+    <t>seriousAlmHighSoc</t>
   </si>
   <si>
     <t>{"en":"Serious alarm due to high SOC"}</t>
@@ -1707,7 +1707,7 @@
     <t>SOC 过高中度报警</t>
   </si>
   <si>
-    <t>socHighModerateAlarm</t>
+    <t>socHighModerateAlm</t>
   </si>
   <si>
     <t>{"en":"SOC high moderate alarm"}</t>
@@ -1716,7 +1716,7 @@
     <t>SOC 过高轻微报警</t>
   </si>
   <si>
-    <t>socHighSlightAlarm</t>
+    <t>socHighSlightAlm</t>
   </si>
   <si>
     <t>{"en":"SOC high slight alarm"}</t>
@@ -1725,7 +1725,7 @@
     <t>SOH 过低严重报警</t>
   </si>
   <si>
-    <t>seriousAlarmForLowSoh</t>
+    <t>seriousAlmLowSoh</t>
   </si>
   <si>
     <t>{"en":"Serious alarm for low SOH"}</t>
@@ -1734,7 +1734,7 @@
     <t>SOH 过低中度报警</t>
   </si>
   <si>
-    <t>sohLowModerateAlarm</t>
+    <t>sohLowModerateAlm</t>
   </si>
   <si>
     <t>{"en":"SOH low moderate alarm"}</t>
@@ -1743,7 +1743,7 @@
     <t>SOH 过低轻微报警</t>
   </si>
   <si>
-    <t>sohLowSlightAlarm</t>
+    <t>sohLowSlightAlm</t>
   </si>
   <si>
     <t>{"en":"SOH low slight alarm"}</t>
@@ -1752,7 +1752,7 @@
     <t>高压箱温度过高严重告警</t>
   </si>
   <si>
-    <t>highVoltageBoxTemperatureSevereAlarm</t>
+    <t>highVBoxTSevereAlm</t>
   </si>
   <si>
     <t>{"en":"High voltage box temperature severe alarm"}</t>
@@ -1761,7 +1761,7 @@
     <t>高压箱温度过高中度告警</t>
   </si>
   <si>
-    <t>highVoltageBoxTemperatureModerateAlarm</t>
+    <t>highVBoxTModerateAlm</t>
   </si>
   <si>
     <t>{"en":"High voltage box temperature moderate alarm"}</t>
@@ -1770,7 +1770,7 @@
     <t>高压箱温度过高轻微告警</t>
   </si>
   <si>
-    <t>highVoltageBoxTemperatureSlightAlarm</t>
+    <t>highVBoxTSlightAlm</t>
   </si>
   <si>
     <t>{"en":"High voltage box temperature slight alarm"}</t>
@@ -1782,7 +1782,7 @@
     <t>mV</t>
   </si>
   <si>
-    <t>seriousAlarmForHighVoltageOfIndividualUnitsInTheGroup</t>
+    <t>seriousAlmHighVCellsInGroup</t>
   </si>
   <si>
     <t>{"en":"Serious alarm for high voltage of individual units in the group"}</t>
@@ -1791,7 +1791,7 @@
     <t>组单体电压过高中度报警</t>
   </si>
   <si>
-    <t>moderateAlarmDueToHighVoltageOfIndividualUnitsInTheGroup</t>
+    <t>moderateAlmHighVCellsInGroup</t>
   </si>
   <si>
     <t>{"en":"Moderate alarm due to high voltage of individual units in the group"}</t>
@@ -1800,7 +1800,7 @@
     <t>组单体电压过高轻微报警</t>
   </si>
   <si>
-    <t>slightAlarmDueToHighVoltageOfIndividualUnitsInTheGroup</t>
+    <t>slightAlmHighVCellsInGroup</t>
   </si>
   <si>
     <t>{"en":"Slight alarm due to high voltage of individual units in the group"}</t>
@@ -1809,7 +1809,7 @@
     <t>单体电压极高报警</t>
   </si>
   <si>
-    <t>singleCellVoltageHighAlarm</t>
+    <t>singleCellVHighAlm</t>
   </si>
   <si>
     <t>{"en":"Single cell voltage high alarm"}</t>
@@ -1818,7 +1818,7 @@
     <t>组单体电压过低严重报警</t>
   </si>
   <si>
-    <t>seriousAlarmForLowVoltageOfIndividualUnitsInTheGroup</t>
+    <t>seriousAlmLowVCellsInGroup</t>
   </si>
   <si>
     <t>{"en":"Serious alarm for low voltage of individual units in the group"}</t>
@@ -1827,7 +1827,7 @@
     <t>组单体电压过低中度报警</t>
   </si>
   <si>
-    <t>moderateAlarmForLowVoltageOfIndividualUnitsInTheGroup</t>
+    <t>moderateAlmLowVCellsInGroup</t>
   </si>
   <si>
     <t>{"en":"Moderate alarm for low voltage of individual units in the group"}</t>
@@ -1836,7 +1836,7 @@
     <t>组单体电压过低轻微报警</t>
   </si>
   <si>
-    <t>slightAlarmForLowVoltageOfIndividualUnitsInTheGroup</t>
+    <t>slightAlmLowVCellsInGroup</t>
   </si>
   <si>
     <t>{"en":"Slight alarm for low voltage of individual units in the group"}</t>
@@ -1845,7 +1845,7 @@
     <t>单体电压极低</t>
   </si>
   <si>
-    <t>extremelyLowIndividualVoltage</t>
+    <t>extremelyLowCellV</t>
   </si>
   <si>
     <t>{"en":"Extremely low individual voltage"}</t>
@@ -1854,7 +1854,7 @@
     <t>组单体压差过大严重报警</t>
   </si>
   <si>
-    <t>seriousAlarmDueToExcessivePressureDifferenceBetweenIndividualUnits</t>
+    <t>seriousAlmExcessCellPressureDiff</t>
   </si>
   <si>
     <t>{"en":"Serious alarm due to excessive pressure difference between individual units"}</t>
@@ -1863,7 +1863,7 @@
     <t>组单体压差过大中度报警</t>
   </si>
   <si>
-    <t>moderateAlarmDueToExcessivePressureDifferenceBetweenIndividualUnits</t>
+    <t>moderateAlmExcessCellPressureDiff</t>
   </si>
   <si>
     <t>{"en":"Moderate alarm due to excessive pressure difference between individual units"}</t>
@@ -1872,7 +1872,7 @@
     <t>组单体压差过大轻微报警</t>
   </si>
   <si>
-    <t>minorAlarmDueToExcessivePressureDifferenceBetweenIndividualUnits</t>
+    <t>minorAlmExcessCellPressureDiff</t>
   </si>
   <si>
     <t>{"en":"Minor alarm due to excessive pressure difference between individual units"}</t>
@@ -1881,7 +1881,7 @@
     <t>组放电温度过高严重报警</t>
   </si>
   <si>
-    <t>severeAlarmForHighDischargeTemperatureInTheGroup</t>
+    <t>severeAlmHighDischgTInGroup</t>
   </si>
   <si>
     <t>{"en":"Severe alarm for high discharge temperature in the group"}</t>
@@ -1890,7 +1890,7 @@
     <t>组放电温度过高中度报警</t>
   </si>
   <si>
-    <t>moderateAlarmForHighGroupDischargeTemperature</t>
+    <t>moderateAlmHighGroupDischgT</t>
   </si>
   <si>
     <t>{"en":"Moderate alarm for high group discharge temperature"}</t>
@@ -1899,7 +1899,7 @@
     <t>组放电温度过高轻微报警</t>
   </si>
   <si>
-    <t>groupDischargeTemperatureTooHighSlightAlarm</t>
+    <t>groupDischgTTooHighSlightAlm</t>
   </si>
   <si>
     <t>{"en":"Group discharge temperature too high, slight alarm"}</t>
@@ -1908,7 +1908,7 @@
     <t>组放电温度过低严重报警</t>
   </si>
   <si>
-    <t>severeAlarmForLowDischargeTemperatureOfTheGroup</t>
+    <t>severeAlmLowDischgTOfGroup</t>
   </si>
   <si>
     <t>{"en":"Severe alarm for low discharge temperature of the group"}</t>
@@ -1917,7 +1917,7 @@
     <t>组放电温度过低中度报警</t>
   </si>
   <si>
-    <t>moderateAlarmForLowGroupDischargeTemperature</t>
+    <t>moderateAlmLowGroupDischgT</t>
   </si>
   <si>
     <t>{"en":"Moderate alarm for low group discharge temperature"}</t>
@@ -1926,7 +1926,7 @@
     <t>组放电温度过低轻微报警</t>
   </si>
   <si>
-    <t>minorAlarmForLowGroupDischargeTemperature</t>
+    <t>minorAlmLowGroupDischgT</t>
   </si>
   <si>
     <t>{"en":"Minor alarm for low group discharge temperature"}</t>
@@ -1935,7 +1935,7 @@
     <t>电池组温差过大严重报警</t>
   </si>
   <si>
-    <t>severeAlarmDueToExcessiveTemperatureDifferenceInBatteryPack</t>
+    <t>severeAlmExcessTDiffInBatteryPack</t>
   </si>
   <si>
     <t>{"en":"Severe alarm due to excessive temperature difference in battery pack"}</t>
@@ -1944,7 +1944,7 @@
     <t>电池组温差过大中度报警</t>
   </si>
   <si>
-    <t>moderateAlarmDueToExcessiveTemperatureDifferenceInBatteryPack</t>
+    <t>moderateAlmExcessTDiffInBatteryPack</t>
   </si>
   <si>
     <t>{"en":"Moderate alarm due to excessive temperature difference in battery pack"}</t>
@@ -1953,7 +1953,7 @@
     <t>电池组温差过大轻微报警</t>
   </si>
   <si>
-    <t>slightAlarmDueToExcessiveTemperatureDifferenceInTheBatteryPack</t>
+    <t>slightAlmExcessTDiffInBatteryPack</t>
   </si>
   <si>
     <t>{"en":"Slight alarm due to excessive temperature difference in the battery pack"}</t>
@@ -1962,7 +1962,7 @@
     <t>电池温升过高严重报警</t>
   </si>
   <si>
-    <t>severeAlarmForHighBatteryTemperatureRise</t>
+    <t>severeAlmHighBatteryTRise</t>
   </si>
   <si>
     <t>{"en":"Severe alarm for high battery temperature rise"}</t>
@@ -1971,7 +1971,7 @@
     <t>电池温升过高中度报警</t>
   </si>
   <si>
-    <t>moderateAlarmForHighBatteryTemperatureRise</t>
+    <t>moderateAlmHighBatteryTRise</t>
   </si>
   <si>
     <t>{"en":"Moderate alarm for high battery temperature rise"}</t>
@@ -1980,7 +1980,7 @@
     <t>电池温升过高轻微报警</t>
   </si>
   <si>
-    <t>slightAlarmForHighBatteryTemperatureRise</t>
+    <t>slightAlmHighBatteryTRise</t>
   </si>
   <si>
     <t>{"en":"Slight alarm for high battery temperature rise"}</t>
@@ -1989,7 +1989,7 @@
     <t>组充电温度过高严重报警</t>
   </si>
   <si>
-    <t>seriousAlarmForHighChargingTemperatureInTheGroup</t>
+    <t>seriousAlmHighChgTInGroup</t>
   </si>
   <si>
     <t>{"en":"Serious alarm for high charging temperature in the group"}</t>
@@ -1998,7 +1998,7 @@
     <t>组充电温度过高中度报警</t>
   </si>
   <si>
-    <t>moderateAlarmForHighChargingTemperatureInTheGroup</t>
+    <t>moderateAlmHighChgTInGroup</t>
   </si>
   <si>
     <t>{"en":"Moderate alarm for high charging temperature in the group"}</t>
@@ -2007,7 +2007,7 @@
     <t>组充电温度过高轻微报警</t>
   </si>
   <si>
-    <t>groupChargingTemperatureTooHighSlightAlarm</t>
+    <t>groupChgTTooHighSlightAlm</t>
   </si>
   <si>
     <t>{"en":"Group charging temperature too high, slight alarm"}</t>
@@ -2016,7 +2016,7 @@
     <t>组充电温度过低严重报警</t>
   </si>
   <si>
-    <t>seriousAlarmForLowChargingTemperatureOfTheGroup</t>
+    <t>seriousAlmLowChgTOfGroup</t>
   </si>
   <si>
     <t>{"en":"Serious alarm for low charging temperature of the group"}</t>
@@ -2025,7 +2025,7 @@
     <t>组充电温度过低中度报警</t>
   </si>
   <si>
-    <t>moderateAlarmForLowGroupChargingTemperature</t>
+    <t>moderateAlmLowGroupChgT</t>
   </si>
   <si>
     <t>{"en":"Moderate alarm for low group charging temperature"}</t>
@@ -2034,7 +2034,7 @@
     <t>组充电温度过低轻微报警</t>
   </si>
   <si>
-    <t>groupChargingTemperatureTooLowSlightAlarm</t>
+    <t>groupChgTTooLowSlightAlm</t>
   </si>
   <si>
     <t>{"en":"Group charging temperature too low, slight alarm"}</t>
@@ -2043,7 +2043,7 @@
     <t>极柱温度过高严重报警</t>
   </si>
   <si>
-    <t>severeAlarmForHighPoleTemperature</t>
+    <t>severeAlmHighPoleT</t>
   </si>
   <si>
     <t>{"en":"Severe alarm for high pole temperature"}</t>
@@ -2052,7 +2052,7 @@
     <t>极柱温度过高中度报警</t>
   </si>
   <si>
-    <t>highPoleTemperatureModerateAlarm</t>
+    <t>highPoleTModerateAlm</t>
   </si>
   <si>
     <t>{"en":"High pole temperature moderate alarm"}</t>
@@ -2061,7 +2061,7 @@
     <t>极柱温度过高轻微报警</t>
   </si>
   <si>
-    <t>slightAlarmForHighPoleTemperature</t>
+    <t>slightAlmHighPoleT</t>
   </si>
   <si>
     <t>{"en":"Slight alarm for high pole temperature"}</t>
@@ -2070,7 +2070,7 @@
     <t>放电电流过大严重报警</t>
   </si>
   <si>
-    <t>seriousAlarmDueToExcessiveDischargeCurrent</t>
+    <t>seriousAlmExcessDischgI</t>
   </si>
   <si>
     <t>{"en":"Serious alarm due to excessive discharge current"}</t>
@@ -2079,7 +2079,7 @@
     <t>放电电流过大中度报警</t>
   </si>
   <si>
-    <t>moderateAlarmDueToExcessiveDischargeCurrent</t>
+    <t>moderateAlmExcessDischgI</t>
   </si>
   <si>
     <t>{"en":"Moderate alarm due to excessive discharge current"}</t>
@@ -2088,7 +2088,7 @@
     <t>放电电流过大轻微报警</t>
   </si>
   <si>
-    <t>minorAlarmDueToExcessiveDischargeCurrent</t>
+    <t>minorAlmExcessDischgI</t>
   </si>
   <si>
     <t>{"en":"Minor alarm due to excessive discharge current"}</t>
@@ -2097,7 +2097,7 @@
     <t>充电电流过大严重报警</t>
   </si>
   <si>
-    <t>seriousAlarmDueToExcessiveChargingCurrent</t>
+    <t>seriousAlmExcessChgI</t>
   </si>
   <si>
     <t>{"en":"Serious alarm due to excessive charging current"}</t>
@@ -2106,7 +2106,7 @@
     <t>充电电流过大中度报警</t>
   </si>
   <si>
-    <t>moderateAlarmDueToExcessiveChargingCurrent</t>
+    <t>moderateAlmExcessChgI</t>
   </si>
   <si>
     <t>{"en":"Moderate alarm due to excessive charging current"}</t>
@@ -2115,7 +2115,7 @@
     <t>充电电流过大轻微报警</t>
   </si>
   <si>
-    <t>minorAlarmDueToExcessiveChargingCurrent</t>
+    <t>minorAlmExcessChgI</t>
   </si>
   <si>
     <t>{"en":"Minor alarm due to excessive charging current"}</t>
@@ -2151,7 +2151,7 @@
     <t>0xFFFF</t>
   </si>
   <si>
-    <t>individualBatteryTemperature</t>
+    <t>cellTemperature</t>
   </si>
   <si>
     <t>{"en":"Individual battery temperature"}</t>
@@ -12569,7 +12569,9 @@
   <dimension ref="A1:S3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" outlineLevelRow="2"/>
   <cols>
-    <col min="1" max="3" width="9" style="2"/>
+    <col min="1" max="1" width="9" style="2"/>
+    <col min="2" max="2" width="11.968253968254" style="2" customWidth="1"/>
+    <col min="3" max="3" width="9" style="2"/>
     <col min="4" max="4" width="13.031746031746" style="2" customWidth="1"/>
     <col min="5" max="5" width="10.6349206349206" style="2" customWidth="1"/>
     <col min="6" max="6" width="13.031746031746" style="2" customWidth="1"/>
